--- a/Assets/Data/DataTable/08_BufDebuf_Table.xlsx
+++ b/Assets/Data/DataTable/08_BufDebuf_Table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32501B3-EE12-45F6-A168-1712F1E2F68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90667400-A460-420D-A7E7-F5BB122C67AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
@@ -341,8 +341,93 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>제동우</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{FB022350-8494-4730-AF95-1AA67BFA8B3D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">0: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">버프
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">1: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>디버프</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{81AE39BB-B183-4FE0-AFD8-EB8EFA7B7F09}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>0: NONE
+1: 공격력
+2: 방어력
+3: SP 보유량
+4: 스피드
+5: 치명타 확률
+6: 치명타 데미지 배율
+7: 카운터 데미지 배율
+8: 속성 게이지 효율 계수
+9: 속성 게이지 저항 계수
+10: 속성 과부하 계수
+11: 받는 피해 증가
+12: 받는 피해 감소
+13: SP 소모량 증가</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="96">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -633,10 +718,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>열거형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -657,18 +738,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Table_</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">버프 디버프 종류 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>공격력, 방어력 등</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1/0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -685,19 +758,42 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>상한 하한</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>재적용 규칙</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>refresh extend atack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정화 가능 불값</t>
+    <t>SP 증가 , 스피드, 공격력, 방어력, 치확, 치뎀, 카운터 데미지, 속성 게이지 효율, 속성 게이지 저항, 속성 과부하, 받는 데미지 증가, 받는 데미지 감소, SP 소모량 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작게 증가, 증가, 크게 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>refresh extend atack-&gt; 더 좋은 걸로 리프레쉬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더하기, 곱하기 등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Table_Buf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버프 카테고리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지속 턴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum:Status_Key:NONE</t>
+  </si>
+  <si>
+    <t>enum:Status_Key:NONE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -705,8 +801,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="179" formatCode="00"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -849,7 +946,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -939,6 +1036,12 @@
     </xf>
     <xf numFmtId="176" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3137,6 +3240,9 @@
   </sheetPr>
   <dimension ref="A2:E18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -3231,6 +3337,9 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
+        <v>95</v>
+      </c>
       <c r="C13" t="s">
         <v>72</v>
       </c>
@@ -3242,17 +3351,17 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -3586,26 +3695,27 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4201226D-AF20-433D-BB3C-B7FD91A16A54}">
-  <dimension ref="A1:H16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4201226D-AF20-433D-BB3C-B7FD91A16A54}">
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="31" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>82</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C1"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>60</v>
@@ -3614,14 +3724,12 @@
         <v>62</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>68</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="F2" s="22"/>
     </row>
     <row r="3" spans="1:8" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -3637,11 +3745,9 @@
         <v>58</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="F3" s="29" t="s">
-        <v>70</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="F3" s="29"/>
     </row>
     <row r="4" spans="1:8" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
@@ -3656,102 +3762,92 @@
       <c r="D4" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>67</v>
-      </c>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="24">
-        <f>(B5*10000000) + (C5*10000) + D5</f>
-        <v>300001001</v>
+        <f>(B5*1000000) + (C5*10000) + D5</f>
+        <v>30001001</v>
       </c>
       <c r="B5" s="24">
         <v>30</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="30">
         <v>0</v>
       </c>
       <c r="D5" s="24">
         <v>1001</v>
       </c>
-      <c r="E5" s="25">
-        <v>100</v>
-      </c>
-      <c r="F5" s="25">
-        <v>1</v>
-      </c>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="24">
-        <f>(B6*10000000) + (C6*10000) + D6</f>
-        <v>300011002</v>
+        <f>(B6*1000000) + (C6*10000) + D6</f>
+        <v>30011002</v>
       </c>
       <c r="B6" s="24">
         <v>30</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="30">
         <v>1</v>
       </c>
       <c r="D6" s="24">
         <v>1002</v>
       </c>
-      <c r="E6" s="25">
-        <v>150</v>
-      </c>
-      <c r="F6" s="25">
-        <v>2</v>
-      </c>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G12" t="s">
-        <v>87</v>
+        <v>93</v>
+      </c>
+      <c r="H12" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G13" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G14" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G16" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
